--- a/artfynd/A 34855-2025 artfynd.xlsx
+++ b/artfynd/A 34855-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>876700</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468428.4243444524</v>
+        <v>468428</v>
       </c>
       <c r="R2" t="n">
-        <v>7093937.092278331</v>
+        <v>7093937</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2011-06-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-06-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>89601375</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468307.0656856341</v>
+        <v>468307</v>
       </c>
       <c r="R3" t="n">
-        <v>7093984.887345448</v>
+        <v>7093985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89601370</v>
+        <v>89601371</v>
       </c>
       <c r="B4" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468289.0822391909</v>
+        <v>468327</v>
       </c>
       <c r="R4" t="n">
-        <v>7093989.902186737</v>
+        <v>7093976</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,19 +951,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,12 +987,7 @@
         <v>89601362</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468328.1011796665</v>
+        <v>468328</v>
       </c>
       <c r="R5" t="n">
-        <v>7093977.20587265</v>
+        <v>7093977</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,19 +1052,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,15 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89601371</v>
+        <v>89601363</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,21 +1096,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468327.2081726633</v>
+        <v>468479</v>
       </c>
       <c r="R6" t="n">
-        <v>7093975.897050475</v>
+        <v>7093983</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,19 +1153,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,6 +1179,107 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>89601370</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brinnsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>468289</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7093990</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
